--- a/artfynd/S 3630-2024 artfynd.xlsx
+++ b/artfynd/S 3630-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96055896</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96055701</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96055821</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1083,6 +1103,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96055877</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1180,6 +1205,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96055738</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1277,6 +1307,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96055794</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1374,6 +1409,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96055679</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1476,6 +1516,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96055678</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1573,6 +1618,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73507836</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1670,6 +1720,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73507837</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1787,6 +1842,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/80519055</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1893,6 +1953,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129425067</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1994,6 +2059,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129424966</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2100,6 +2170,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73282830</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2201,6 +2276,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129425097</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2298,6 +2378,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73282832</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2400,6 +2485,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129424983</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2506,6 +2596,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73282825</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2612,6 +2707,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73282831</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2718,6 +2818,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73282833</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2819,6 +2924,11 @@
           <t>Värdefulla skogsmiljöer i Västmanlands län</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129425027</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2930,6 +3040,11 @@
           <t>Trafikverkets inventeringar av arter i statliga vägmiljöer</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72871285</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3041,6 +3156,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102673742</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3138,6 +3258,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/388339</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3247,6 +3372,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82030431</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3378,6 +3508,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89093087</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3491,6 +3626,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70662305</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3597,6 +3737,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7120999</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3706,8 +3851,44 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104284697</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 3630-2024 artfynd.xlsx
+++ b/artfynd/S 3630-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ30"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3164,10 +3164,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>388339</v>
+        <v>136326066</v>
       </c>
       <c r="B25" t="n">
-        <v>84147</v>
+        <v>106478</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3175,37 +3175,45 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1444</v>
+        <v>221157</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Scharlakansvårskål agg.</t>
+          <t>Blåbär</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Sarcoscypha coccinea s.lat.</t>
+          <t>Vaccinium myrtillus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Jacq.:Fr.) Lambotte</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Rotsjön väster, Vstm</t>
+          <t>Kolsva, körväg 235m SV infart, 50m SO korsning kraftledning, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>545395</v>
+        <v>545165</v>
       </c>
       <c r="R25" t="n">
-        <v>6605002</v>
+        <v>6607889</v>
       </c>
       <c r="S25" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3229,12 +3237,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2010-04-25</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2010-04-25</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3243,33 +3251,34 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Tina Nordberg</t>
+          <t>Eva Milton</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Tina Nordberg</t>
+          <t>Eva Milton</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/388339</t>
+          <t>https://artportalen.se/Sighting/136326066</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>82030431</v>
+        <v>136326057</v>
       </c>
       <c r="B26" t="n">
-        <v>84147</v>
+        <v>107820</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3277,48 +3286,41 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1444</v>
+        <v>224273</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Scharlakansvårskål agg.</t>
+          <t>Vanlig ängskovall</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Sarcoscypha coccinea s.lat.</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Jacq.:Fr.) Lambotte</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
+          <t>Melampyrum pratense var. pratense</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>V Rotsjön, Vstm</t>
+          <t>Kolsva, körväg 235m SV infart, 50m SO korsning kraftledning, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>545436</v>
+        <v>545165</v>
       </c>
       <c r="R26" t="n">
-        <v>6605100</v>
+        <v>6607889</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3342,12 +3344,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2020-02-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2020-02-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3363,27 +3365,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kenneth Nordberg</t>
+          <t>Eva Milton</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kenneth Nordberg, Tina Nordberg</t>
+          <t>Eva Milton</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/82030431</t>
+          <t>https://artportalen.se/Sighting/136326057</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>89093087</v>
+        <v>388339</v>
       </c>
       <c r="B27" t="n">
-        <v>58817</v>
+        <v>84147</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3391,56 +3393,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>208249</v>
+        <v>1444</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>trafikdödad</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>lampa</t>
-        </is>
-      </c>
+          <t>(Jacq.:Fr.) Lambotte</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Rotsjön, Vstm</t>
+          <t>Rotsjön väster, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>545371</v>
+        <v>545395</v>
       </c>
       <c r="R27" t="n">
-        <v>6605035</v>
+        <v>6605002</v>
       </c>
       <c r="S27" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3464,27 +3447,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2020-04-14</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>22:00</t>
+          <t>2010-04-25</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2020-04-15</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>04:00</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Trafikverkets arbete med konfliktpunkter</t>
+          <t>2010-04-25</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3499,27 +3467,27 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Daniel Segerlind</t>
+          <t>Tina Nordberg</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Daniel Segerlind, Barbara Kühn, Tor Hansson Frank, André Dabolins</t>
+          <t>Tina Nordberg</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89093087</t>
+          <t>https://artportalen.se/Sighting/388339</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>70662305</v>
+        <v>82030431</v>
       </c>
       <c r="B28" t="n">
-        <v>84148</v>
+        <v>84147</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3527,26 +3495,26 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>232272</v>
+        <v>1444</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Scharlakansskål</t>
+          <t>Scharlakansvårskål agg.</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sarcoscypha austriaca</t>
+          <t>Sarcoscypha coccinea s.lat.</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Beck) Boud.</t>
+          <t>(Jacq.:Fr.) Lambotte</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -3555,19 +3523,20 @@
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Rotsjön väster, Vstm</t>
+          <t>V Rotsjön, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>545395</v>
+        <v>545436</v>
       </c>
       <c r="R28" t="n">
-        <v>6605002</v>
+        <v>6605100</v>
       </c>
       <c r="S28" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3591,12 +3560,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2018-04-16</t>
+          <t>2020-02-04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2018-04-16</t>
+          <t>2020-02-04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3609,15 +3578,10 @@
       <c r="AG28" t="b">
         <v>0</v>
       </c>
-      <c r="AI28" t="inlineStr">
-        <is>
-          <t>Strandnära blandskog</t>
-        </is>
-      </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Tina Nordberg</t>
+          <t>Kenneth Nordberg</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -3628,55 +3592,70 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/70662305</t>
+          <t>https://artportalen.se/Sighting/82030431</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>7120999</v>
+        <v>89093087</v>
       </c>
       <c r="B29" t="n">
-        <v>93233</v>
+        <v>58817</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5964</v>
+        <v>208249</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>trafikdödad</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>lampa</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Kolsva, Vstm</t>
+          <t>Rotsjön, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544457</v>
+        <v>545371</v>
       </c>
       <c r="R29" t="n">
-        <v>6604939</v>
+        <v>6605035</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3703,17 +3682,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2011-09-13</t>
+          <t>2020-04-14</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>22:00</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2011-09-13</t>
+          <t>2020-04-15</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Sveaskogs Naturvärdesinventering -Inventerare: Emil P A  ID;29903</t>
+          <t>Trafikverkets arbete med konfliktpunkter</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3728,77 +3717,75 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Daniel Segerlind</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Sveaskog genom Johan Ekenstedt</t>
+          <t>Daniel Segerlind, Barbara Kühn, Tor Hansson Frank, André Dabolins</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/7120999</t>
+          <t>https://artportalen.se/Sighting/89093087</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>104284697</v>
+        <v>70662305</v>
       </c>
       <c r="B30" t="n">
-        <v>58114</v>
+        <v>84148</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>232272</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Scharlakansskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcoscypha austriaca</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Beck) Boud.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>V Svansjön, Vstm</t>
+          <t>Rotsjön väster, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544347</v>
+        <v>545395</v>
       </c>
       <c r="R30" t="n">
-        <v>6604615</v>
+        <v>6605002</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3822,12 +3809,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2018-04-16</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-10-23</t>
+          <t>2018-04-16</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3836,13 +3823,19 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Strandnära blandskog</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kenneth Nordberg</t>
+          <t>Tina Nordberg</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
@@ -3852,6 +3845,231 @@
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/70662305</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>7120999</v>
+      </c>
+      <c r="B31" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Kolsva, Vstm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>544457</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6604939</v>
+      </c>
+      <c r="S31" t="n">
+        <v>5</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Kolsva</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2011-09-13</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2011-09-13</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Sveaskogs Naturvärdesinventering -Inventerare: Emil P A  ID;29903</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Sveaskog genom Johan Ekenstedt</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Sveaskog genom Johan Ekenstedt</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/7120999</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>104284697</v>
+      </c>
+      <c r="B32" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>V Svansjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>544347</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6604615</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Köping</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Kolsva</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2022-10-23</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2022-10-23</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Kenneth Nordberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Kenneth Nordberg, Tina Nordberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/104284697</t>
         </is>
@@ -3888,6 +4106,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 3630-2024 artfynd.xlsx
+++ b/artfynd/S 3630-2024 artfynd.xlsx
@@ -3167,7 +3167,7 @@
         <v>136326066</v>
       </c>
       <c r="B25" t="n">
-        <v>106478</v>
+        <v>106489</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>136326057</v>
       </c>
       <c r="B26" t="n">
-        <v>107820</v>
+        <v>107831</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 3630-2024 artfynd.xlsx
+++ b/artfynd/S 3630-2024 artfynd.xlsx
@@ -3167,7 +3167,7 @@
         <v>136326066</v>
       </c>
       <c r="B25" t="n">
-        <v>106489</v>
+        <v>106502</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>136326057</v>
       </c>
       <c r="B26" t="n">
-        <v>107831</v>
+        <v>107844</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 3630-2024 artfynd.xlsx
+++ b/artfynd/S 3630-2024 artfynd.xlsx
@@ -3167,7 +3167,7 @@
         <v>136326066</v>
       </c>
       <c r="B25" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>136326057</v>
       </c>
       <c r="B26" t="n">
-        <v>107844</v>
+        <v>107845</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 3630-2024 artfynd.xlsx
+++ b/artfynd/S 3630-2024 artfynd.xlsx
@@ -3167,7 +3167,7 @@
         <v>136326066</v>
       </c>
       <c r="B25" t="n">
-        <v>106503</v>
+        <v>106516</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>136326057</v>
       </c>
       <c r="B26" t="n">
-        <v>107845</v>
+        <v>107858</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/S 3630-2024 artfynd.xlsx
+++ b/artfynd/S 3630-2024 artfynd.xlsx
@@ -3167,7 +3167,7 @@
         <v>136326066</v>
       </c>
       <c r="B25" t="n">
-        <v>106516</v>
+        <v>106517</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3278,7 +3278,7 @@
         <v>136326057</v>
       </c>
       <c r="B26" t="n">
-        <v>107858</v>
+        <v>107859</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
